--- a/data/trans_orig/P20B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16696</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37858</t>
+          <t>37749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>30884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41664</t>
+          <t>41671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>19852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30725</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16696</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>33443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36770</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55467</t>
+          <t>55002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85586</t>
+          <t>84987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101734</t>
+          <t>102013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25276</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35801</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>48214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13075</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>28124</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>13733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51905</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67279</t>
+          <t>67261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54311</t>
+          <t>55590</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70328</t>
+          <t>70240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45688</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69951</t>
+          <t>71546</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102057</t>
+          <t>102438</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88294</t>
+          <t>88128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108708</t>
+          <t>107860</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>185435</t>
+          <t>186288</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>209426</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280292</t>
+          <t>279911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>312398</t>
+          <t>310803</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>14711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29255</t>
+          <t>28674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31164</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45179</t>
+          <t>46097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32196</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38639</t>
+          <t>37765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48102</t>
+          <t>47909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25560</t>
+          <t>26118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19878</t>
+          <t>19930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41282</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56851</t>
+          <t>57675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31917</t>
+          <t>32279</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50219</t>
+          <t>50228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58293</t>
+          <t>58364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55700</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70409</t>
+          <t>71069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102846</t>
+          <t>102837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124363</t>
+          <t>124472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36806</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>51933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30336</t>
+          <t>30484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42234</t>
+          <t>40832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>59537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63565</t>
+          <t>65204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87370</t>
+          <t>85903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>29217</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>55752</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72212</t>
+          <t>72128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60406</t>
+          <t>61379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77198</t>
+          <t>77383</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48649</t>
+          <t>48214</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76947</t>
+          <t>76082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67250</t>
+          <t>65961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100738</t>
+          <t>98844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123981</t>
+          <t>122828</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166002</t>
+          <t>168984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>128807</t>
+          <t>129672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>157105</t>
+          <t>157540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231642</t>
+          <t>233536</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>265130</t>
+          <t>266419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>372132</t>
+          <t>369150</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>414153</t>
+          <t>415306</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016 (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>24606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38860</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52094</t>
+          <t>52246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19565</t>
+          <t>19543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>29419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47593</t>
+          <t>47198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,61%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24937</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14953</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>25976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>22825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>29496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25735</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47162</t>
+          <t>47199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>38857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52418</t>
+          <t>52222</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66339</t>
+          <t>66827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80598</t>
+          <t>80561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102025</t>
+          <t>101224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>35493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33957</t>
+          <t>34349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50433</t>
+          <t>49816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23169</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>24268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>43949</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50457</t>
+          <t>50998</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66097</t>
+          <t>66595</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>67203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>50800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79847</t>
+          <t>81415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101246</t>
+          <t>102423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96117</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119975</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>189684</t>
+          <t>188116</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217828</t>
+          <t>218731</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>291088</t>
+          <t>289558</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>330762</t>
+          <t>329585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23062</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30370</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>38907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51679</t>
+          <t>51902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21062</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>18206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41132</t>
+          <t>40579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14069</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35422</t>
+          <t>35044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,66%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21231</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>31845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51332</t>
+          <t>51196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>38109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>46979</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79654</t>
+          <t>80398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95669</t>
+          <t>96041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33812</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>21171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>32518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>23046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>32859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>47269</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61854</t>
+          <t>62273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35165</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>49540</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75315</t>
+          <t>74487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37799</t>
+          <t>38307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61642</t>
+          <t>60255</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94374</t>
+          <t>94406</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128147</t>
+          <t>128721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112031</t>
+          <t>112859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137008</t>
+          <t>137806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148797</t>
+          <t>150184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>172640</t>
+          <t>172132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269638</t>
+          <t>269064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>303411</t>
+          <t>303379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37749</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28326</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30884</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>41684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>30818</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>33361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>36744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49157</t>
+          <t>49134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>43597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55002</t>
+          <t>55545</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84987</t>
+          <t>85069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102013</t>
+          <t>102053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36492</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36130</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>48586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28124</t>
+          <t>28169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>52185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67261</t>
+          <t>67332</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55590</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70240</t>
+          <t>70130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>63528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71546</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102438</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88128</t>
+          <t>88556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186288</t>
+          <t>184839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>211612</t>
+          <t>209743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>279911</t>
+          <t>279846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>311987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14711</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28674</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46097</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32265</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>47636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26118</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>39357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57675</t>
+          <t>56875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32279</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>23345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50228</t>
+          <t>48971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41373</t>
+          <t>41280</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58364</t>
+          <t>58089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>56068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71069</t>
+          <t>70212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102837</t>
+          <t>104094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124472</t>
+          <t>125006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>36817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>52077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40832</t>
+          <t>42223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59537</t>
+          <t>58741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65204</t>
+          <t>65060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85903</t>
+          <t>86721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15862</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>32068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55752</t>
+          <t>55922</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72128</t>
+          <t>72950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61379</t>
+          <t>60780</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77383</t>
+          <t>76986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>48631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76082</t>
+          <t>75956</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65961</t>
+          <t>66810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98844</t>
+          <t>98551</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122828</t>
+          <t>123610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168984</t>
+          <t>164299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129672</t>
+          <t>129798</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>157540</t>
+          <t>157123</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>233536</t>
+          <t>233829</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>266419</t>
+          <t>265570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>369150</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>415306</t>
+          <t>414524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24606</t>
+          <t>24827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39580</t>
+          <t>39536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52246</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,95%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19543</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>29356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34353</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47198</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17066</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25976</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22825</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36435</t>
+          <t>37242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29496</t>
+          <t>28304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>47535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38857</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52222</t>
+          <t>51140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66827</t>
+          <t>65849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80561</t>
+          <t>80225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101224</t>
+          <t>101787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25777</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35493</t>
+          <t>35402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>17732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34349</t>
+          <t>34355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>33172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49816</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>43402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58105</t>
+          <t>57781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50998</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66595</t>
+          <t>65978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67203</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50800</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>81571</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102423</t>
+          <t>101805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142450</t>
+          <t>140282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95274</t>
+          <t>93986</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120658</t>
+          <t>119183</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188116</t>
+          <t>187960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>218731</t>
+          <t>216722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>289558</t>
+          <t>291726</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>329585</t>
+          <t>330203</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>20025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10769</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>25797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28267</t>
+          <t>32574</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>28868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>34984</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>46106</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38907</t>
+          <t>43300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51902</t>
+          <t>57728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>62671</t>
+          <t>69097</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62671</t>
+          <t>69097</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62671</t>
+          <t>69097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>11840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>27549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>35665</t>
+          <t>39167</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28849</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40579</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>19273</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22842</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>28818</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35044</t>
+          <t>39502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>71,45%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>34264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>45700</t>
+          <t>48544</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38778</t>
+          <t>41593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43327</t>
+          <t>49255</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46979</t>
+          <t>53653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>89027</t>
+          <t>97798</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80398</t>
+          <t>88503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96041</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>112243</t>
+          <t>122767</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>112243</t>
+          <t>122767</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112243</t>
+          <t>122767</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>20619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,67 +10040,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>33,2%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>22,54%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>45,32%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>29495</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>22279</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>38676</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>32,45%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>44,62%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>26312</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>19048</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>34052</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26895</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>23481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32518</t>
+          <t>35322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,67 +10153,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>25590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>36247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>66,8%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>54,68%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>77,46%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>61400</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>52219</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>68616</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>67,55%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>55,38%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>78,96%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>55009</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>47269</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>62273</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>67,64%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30637</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35431</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>36734</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>27990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37778</t>
+          <t>41722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>43891</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>43891</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>43891</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>48051</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>48051</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>48051</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49540</t>
+          <t>54583</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74487</t>
+          <t>82018</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38307</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60255</t>
+          <t>67943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>104931</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128721</t>
+          <t>141284</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>125069</t>
+          <t>136180</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112859</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137806</t>
+          <t>149799</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>162553</t>
+          <t>183228</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150184</t>
+          <t>170453</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>172132</t>
+          <t>194487</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>287623</t>
+          <t>319407</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269064</t>
+          <t>301493</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>303379</t>
+          <t>337846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>187346</t>
+          <t>204382</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>187346</t>
+          <t>204382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>187346</t>
+          <t>204382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>210439</t>
+          <t>238396</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>210439</t>
+          <t>238396</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>210439</t>
+          <t>238396</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>397785</t>
+          <t>442777</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>397785</t>
+          <t>442777</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>397785</t>
+          <t>442777</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
